--- a/쿠팡_11개카테고리_275개_제품목록.xlsx
+++ b/쿠팡_11개카테고리_275개_제품목록.xlsx
@@ -4211,7 +4211,11 @@
           <t>탐사 베이킹소다 주방세제 레몬향</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/323587276</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>5490</v>
       </c>
@@ -4320,7 +4324,11 @@
           <t>퐁퐁 오렌지 오일 담은 친환경 주방세제 기분 좋은 오렌지향 리필</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9716584862</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>4700</v>
       </c>
@@ -4429,7 +4437,11 @@
           <t>퐁퐁 베이킹소다 주방세제 깔끔한 민트향 리필형</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9737456493</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>5650</v>
       </c>
@@ -4538,7 +4550,11 @@
           <t>트리오 항균 주방세제</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6499690442</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>15890</v>
       </c>
@@ -4652,7 +4668,11 @@
           <t>참그린 레몬 녹차 뽀드득 어드밴스 주방세제 리필</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7867434239</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>8930</v>
       </c>
@@ -4761,7 +4781,11 @@
           <t>탐사 클린퐁 주방세제</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7835456914</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>9780</v>
       </c>
@@ -4870,7 +4894,11 @@
           <t>탐사 주방세제 리필</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6631315054</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>4280</v>
       </c>
@@ -4979,7 +5007,11 @@
           <t>주방세제 베이킹소다 과일 야채 식기세척 대용량 주방 세제</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9629569396</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>6920</v>
       </c>
@@ -5088,7 +5120,11 @@
           <t>프릴 시크릿오브 베이킹소다 주방세제 상큼한 오렌지향</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8189756332?itemId=23433588846&amp;vendorItemId=90460524397</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>8130</v>
       </c>
@@ -5197,7 +5233,11 @@
           <t>주방용 세제 베이킹소다 주방세제 레몬향</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9701090891</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>4670</v>
       </c>
@@ -5306,7 +5346,11 @@
           <t>크로바 골드퐁 주방세제</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9028328561</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>10750</v>
       </c>
@@ -5415,7 +5459,11 @@
           <t>자연퐁 스팀워시 식기세척기용 액체세제</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7325899154?itemId=19713363478&amp;vendorItemId=88356717131</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>13980</v>
       </c>
@@ -5529,7 +5577,11 @@
           <t>주방세제 베이킹소다 대용량주방세제 레몬향</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9577065924</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>7080</v>
       </c>
@@ -5643,7 +5695,11 @@
           <t>프릴 시크릿오브 베이킹소다 주방세제 상큼한 오렌지향</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8202659515</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>7540</v>
       </c>
@@ -5757,7 +5813,11 @@
           <t>프로쉬 식기세척기 린스</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8627561762?itemId=25248625355&amp;vendorItemId=92416024733</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>12300</v>
       </c>
@@ -5871,7 +5931,11 @@
           <t>탐사 라임 주방세제</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7632373677</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>6500</v>
       </c>
@@ -5980,7 +6044,11 @@
           <t>슈가버블 친환경 주방세제 레몬 크러쉬</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7136884232</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>3900</v>
       </c>
@@ -6094,7 +6162,11 @@
           <t>[비건라이프] 자연퐁 찌든때 걱정없는 솔잎 주방세제 용기형 리필</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7878925549</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>15100</v>
       </c>
@@ -6203,7 +6275,11 @@
           <t>프로쉬 주방세제 알로에베라</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8403347749</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>5590</v>
       </c>
@@ -6317,7 +6393,11 @@
           <t>트리오 베이킹소다 담은 퓨어허브향 주방세제</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9707279838</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>3200</v>
       </c>
@@ -6431,7 +6511,11 @@
           <t>자연퐁 찌든때 걱정없는 솔잎 파워워시 주방세제 용기형</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7925775685</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>9100</v>
       </c>
@@ -6540,7 +6624,11 @@
           <t>맘스럽 레몬 주방세제 베이킹소다 특대용량 레몬향 과일 채소용 중성 세제</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9305171629</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>7140</v>
       </c>
@@ -6649,7 +6737,11 @@
           <t>[비건라이프] 세이프 천연미네랄 주방세제 오리지널</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/80924</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>11050</v>
       </c>
@@ -6758,7 +6850,11 @@
           <t>뷰카 베이킹소다 주방세제 레몬버베나향</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7589391826</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>13560</v>
       </c>
@@ -6867,7 +6963,11 @@
           <t>트리오 베이킹소다를 담은 주방세제</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7031130231</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>8450</v>
       </c>
@@ -7122,7 +7222,11 @@
           <t>피지 모락셀라 냄새제거 부스터 캡슐 뽀송한 코튼향</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8468431077?itemId=24501177230&amp;vendorItemId=91514259719</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>14160</v>
       </c>
@@ -7231,7 +7335,11 @@
           <t>허글리 8IN1 딥 클린 초고농축 캡슐 세탁세제 코튼캔디 향</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8687771994</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>13910</v>
       </c>
@@ -7340,7 +7448,11 @@
           <t>퍼실 뉴 디스크 프로 플러스 캡슐세제</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9131334002</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>19800</v>
       </c>
@@ -7449,7 +7561,11 @@
           <t>버블업 딥 클린 초고농축 캡슐세탁세제 120개입</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9522535018</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>6900</v>
       </c>
@@ -7563,7 +7679,11 @@
           <t>맘스럽 울트라 퍼퓸 캡슐세제 16gX100개입 8배 초고농축 3in1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7826482313</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>8730</v>
       </c>
@@ -7677,7 +7797,11 @@
           <t>맘스럽 퍼펙트 캡슐세제 4챔버 파우치형 8배 초고농축 4in1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8641935458</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>8610</v>
       </c>
@@ -7786,7 +7910,11 @@
           <t>캡슐세제 캡슐세탁세제 라벤더향 캡슐 세제</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9616382867</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>5890</v>
       </c>
@@ -7900,7 +8028,11 @@
           <t>퍼실 뉴 디스크 파워 플러스 캡슐세제</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8512394860</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>12790</v>
       </c>
@@ -8014,7 +8146,11 @@
           <t>부케가르니 딥 클린 초고농축 캡슐세제</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7871650750</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>10940</v>
       </c>
@@ -8123,7 +8259,11 @@
           <t>랩신 냄새 제거 부스터 무향 캡슐 세제</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8812083389</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>12440</v>
       </c>
@@ -8237,7 +8377,11 @@
           <t>액츠 멀티 솔루션 실내건조 컴팩트 캡슐세제</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8769278546</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>12330</v>
       </c>
@@ -8346,7 +8490,11 @@
           <t>소소이지 이지 캡슐 세제 그리너리 머스크</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6583484325</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>20890</v>
       </c>
@@ -8455,7 +8603,11 @@
           <t>스너글 블루스파클 플러스 실내건조 캡슐세제</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7771483156</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>10600</v>
       </c>
@@ -8564,7 +8716,11 @@
           <t>카포드 센트라린 듀얼코어 캡슐세제</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6939963919</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>17480</v>
       </c>
@@ -8673,7 +8829,11 @@
           <t>쉬슬러 울트라 액티브 초고농축 캡슐세제 릴리향</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9116099134</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>8580</v>
       </c>
@@ -8787,7 +8947,11 @@
           <t>피지 모락셀라 냄새제거 부스터 캡슐 상쾌한 허브향</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8252830879</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>14630</v>
       </c>
@@ -8901,7 +9065,11 @@
           <t>피지 모락셀라 실내건조 냄새제거 부스터 캡슐세제 화이트머스크향</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9219560266</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>14950</v>
       </c>
@@ -9010,7 +9178,11 @@
           <t>퍼실 디스크 컬러 캡슐세제 파우치</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8173755589</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>17070</v>
       </c>
@@ -9119,7 +9291,11 @@
           <t>퍼실 뉴 디스크 라벤더 플러스 캡슐세제</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8173755589</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>37300</v>
       </c>
@@ -9233,7 +9409,11 @@
           <t>스너글 허거블 코튼 클린 앤 케어 캡슐세제</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7771483157?itemId=28604973749&amp;vendorItemId=95548520771</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>20000</v>
       </c>
@@ -9347,7 +9527,11 @@
           <t>올클린 냄새제거 초고농축 캡슐 세탁세제</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9655016135</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>7800</v>
       </c>
@@ -9461,7 +9645,11 @@
           <t>비트 캡슐 실내건조 캡슐세제 그린 플로럴향</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7674477942</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>13530</v>
       </c>
@@ -9570,7 +9758,11 @@
           <t>리큐 모락셀라 악취케어 실내건조 캡슐세제</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9726339807</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>12290</v>
       </c>
@@ -9684,7 +9876,11 @@
           <t>[커클랜드 시그니처] 커클랜드 울트라클린팩세제 140PC</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8363764498</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>29990</v>
       </c>
@@ -9798,7 +9994,11 @@
           <t>테크 딥클린 초고농축 캡슐세제</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8710604087</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>9810</v>
       </c>
@@ -11592,7 +11792,11 @@
           <t>아로퓸 향기 부스터 허니드 엑스트라, 500g, 1개</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8308867067</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>11950</v>
       </c>
@@ -12060,7 +12264,11 @@
           <t>아로퓸 향기 부스터 스윗 샤인, 500g, 1개</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8308872271?itemId=23973816647&amp;vendorItemId=88684518486</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>11950</v>
       </c>
@@ -13146,7 +13354,11 @@
           <t>피지 모락셀라 냄새제거 세탁세제 코튼향</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8527004003</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>14650</v>
       </c>
@@ -13260,7 +13472,11 @@
           <t>탐사 파워워시 액체세제 본품</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/305732568</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>10990</v>
       </c>
@@ -13369,7 +13585,11 @@
           <t>액츠 퍼펙트 실내건조 일반용 프레시 플로럴향 액상세제 본품</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9711973763</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>9590</v>
       </c>
@@ -13478,7 +13698,11 @@
           <t>퍼실 딥클린 초미세세탁 라벤더젤 맥스 드럼용 액체세제 본품</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8971726601</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>13940</v>
       </c>
@@ -13587,7 +13811,11 @@
           <t>퍼실 딥클린 초미세세탁 라벤더젤 맥스 일반용 액체세제 리필</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9354349642</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>14920</v>
       </c>
@@ -13701,7 +13929,11 @@
           <t>피지 모락셀라 빨래쉰내 냄새제거 실내건조 세탁세제 코튼향 리필</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8542806480</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>14950</v>
       </c>
@@ -13810,7 +14042,11 @@
           <t>세탁세제 실내건조 라벤더향 액체세제 일반용 드럼용 세제</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9618034717</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>7570</v>
       </c>
@@ -13924,7 +14160,11 @@
           <t>리큐 진한겔 하이브리드 플로랄향 일반용 액상세제 리필</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6616908158</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>18900</v>
       </c>
@@ -14033,7 +14273,11 @@
           <t>세탁세제 실내건조 액체세제 일반용 드럼용 세제</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9614568860</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>6980</v>
       </c>
@@ -14147,7 +14391,11 @@
           <t>스너글 블루스파클 플러스 실내건조 액상세탁세제 본품</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8457659514</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>14910</v>
       </c>
@@ -14256,7 +14504,11 @@
           <t>액체세제 빨래세제 실내건조 중성 액체 세탁 세제</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9116096390</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>7660</v>
       </c>
@@ -14370,7 +14622,11 @@
           <t>피지 모락셀라 실내건조 냄새제거 세탁세제 화이트머스크향 본품</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9219436965?itemId=27242368652&amp;vendorItemId=95181766755</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>14950</v>
       </c>
@@ -14479,7 +14735,11 @@
           <t>다우니 실내건조 초고농축 섬유유연제 프레시 클린 자스민향 리필</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8773985820?itemId=25523705270&amp;vendorItemId=91855119935</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>21990</v>
       </c>
@@ -14593,7 +14853,11 @@
           <t>비트 진드기 침투세탁 액상세제 일반용 본품</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/990781?itemId=17746812132&amp;vendorItemId=3000206661</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>31550</v>
       </c>
@@ -14707,7 +14971,11 @@
           <t>터치 라이트 고농축 세탁세제 라벤더</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8034891009</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>14750</v>
       </c>
@@ -14821,7 +15089,11 @@
           <t>퍼실 딥클린 초미세세탁 파워젤 맥스 드럼용 액체세제 본품</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9354362095</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>13850</v>
       </c>
@@ -14930,7 +15202,11 @@
           <t>봉쥬르끌레어 블랙젤 액체세제 라벤더향 실내건조 중성세제</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8416837413</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>6990</v>
       </c>
@@ -15039,7 +15315,11 @@
           <t>비트 때가쏙 진드기 일반 액상세제 리필</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/2299858861</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>19870</v>
       </c>
@@ -15148,7 +15428,11 @@
           <t>탐사 딥클린 코튼향 세탁세제 본품</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8915603116</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>4950</v>
       </c>
@@ -15257,7 +15541,11 @@
           <t>테크 베이킹소다 플러스 구연산 실내건조 액체세제 일반용 리필</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7825605298</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>17910</v>
       </c>
@@ -15366,7 +15654,11 @@
           <t>퍼실 엑스퍼트 실내건조 맥스 드럼용 액상세제 본품</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9414661283?itemId=27974996303&amp;vendorItemId=94932853898</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>13770</v>
       </c>
@@ -15475,7 +15767,11 @@
           <t>터치 고농축 액체세제 코델리아 세탁세제 3.05L 4개</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7206437724?itemId=18225908031&amp;vendorItemId=85155981677</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>19650</v>
       </c>
@@ -15584,7 +15880,11 @@
           <t>액츠 퍼펙트 실내건조 액상세제 리필</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8123764928</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>20700</v>
       </c>
@@ -15693,7 +15993,11 @@
           <t>리큐 진한겔 하이브리드 드럼세탁기용 액상세제 플로럴 부케향 리필</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7235489530</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>18900</v>
       </c>
@@ -15802,7 +16106,11 @@
           <t>퍼실 딥클린 초미세세탁 라벤더젤 맥스 일반용 액체세제 본품</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9354362095?itemId=27967268511&amp;vendorItemId=94925214636</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>13940</v>
       </c>
@@ -15911,7 +16219,11 @@
           <t>피지 모락셀라 냄새제거 부스터 캡슐 뽀송한 코튼향</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8468431077?itemId=24501177230&amp;vendorItemId=91514259719</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>14160</v>
       </c>
@@ -16020,7 +16332,11 @@
           <t>허글리 8IN1 딥 클린 초고농축 캡슐 세탁세제 코튼캔디 향</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8687771994</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>13910</v>
       </c>
@@ -16129,7 +16445,11 @@
           <t>퍼실 뉴 디스크 프로 플러스 캡슐세제</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9131334002</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>19800</v>
       </c>
@@ -16238,7 +16558,11 @@
           <t>버블업 딥 클린 초고농축 캡슐세탁세제 120개입</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9522535018</t>
+        </is>
+      </c>
       <c r="H30" t="n">
         <v>6900</v>
       </c>
@@ -16352,7 +16676,11 @@
           <t>맘스럽 울트라 퍼퓸 캡슐세제 16gX100개입 8배 초고농축 3in1</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7826482313</t>
+        </is>
+      </c>
       <c r="H31" t="n">
         <v>8730</v>
       </c>
@@ -16466,7 +16794,11 @@
           <t>맘스럽 퍼펙트 캡슐세제 4챔버 파우치형 8배 초고농축 4in1</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8641935458</t>
+        </is>
+      </c>
       <c r="H32" t="n">
         <v>8610</v>
       </c>
@@ -16575,7 +16907,11 @@
           <t>캡슐세제 캡슐세탁세제 라벤더향 캡슐 세제</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9616382867</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>5890</v>
       </c>
@@ -16689,7 +17025,11 @@
           <t>퍼실 뉴 디스크 파워 플러스 캡슐세제</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8512394860</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>12790</v>
       </c>
@@ -16803,7 +17143,11 @@
           <t>부케가르니 딥 클린 초고농축 캡슐세제</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7871650750</t>
+        </is>
+      </c>
       <c r="H35" t="n">
         <v>10940</v>
       </c>
@@ -16912,7 +17256,11 @@
           <t>랩신 냄새 제거 부스터 무향 캡슐 세제</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8812083389</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>12440</v>
       </c>
@@ -17026,7 +17374,11 @@
           <t>액츠 멀티 솔루션 실내건조 컴팩트 캡슐세제</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8769278546</t>
+        </is>
+      </c>
       <c r="H37" t="n">
         <v>12330</v>
       </c>
@@ -17135,7 +17487,11 @@
           <t>소소이지 이지 캡슐 세제 그리너리 머스크</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6583484325</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>20890</v>
       </c>
@@ -17244,7 +17600,11 @@
           <t>스너글 블루스파클 플러스 실내건조 캡슐세제</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7771483156</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>10600</v>
       </c>
@@ -17353,7 +17713,11 @@
           <t>카포드 센트라린 듀얼코어 캡슐세제</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6939963919</t>
+        </is>
+      </c>
       <c r="H40" t="n">
         <v>17480</v>
       </c>
@@ -17462,7 +17826,11 @@
           <t>쉬슬러 울트라 액티브 초고농축 캡슐세제 릴리향</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9116099134</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>8580</v>
       </c>
@@ -17576,7 +17944,11 @@
           <t>피지 모락셀라 냄새제거 부스터 캡슐 상쾌한 허브향</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8252830879</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>14630</v>
       </c>
@@ -17690,7 +18062,11 @@
           <t>피지 모락셀라 실내건조 냄새제거 부스터 캡슐세제 화이트머스크향</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9219560266</t>
+        </is>
+      </c>
       <c r="H43" t="n">
         <v>14950</v>
       </c>
@@ -17799,7 +18175,11 @@
           <t>퍼실 디스크 컬러 캡슐세제 파우치</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8173755589</t>
+        </is>
+      </c>
       <c r="H44" t="n">
         <v>17070</v>
       </c>
@@ -17908,7 +18288,11 @@
           <t>퍼실 뉴 디스크 라벤더 플러스 캡슐세제</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8173755589</t>
+        </is>
+      </c>
       <c r="H45" t="n">
         <v>37300</v>
       </c>
@@ -18022,7 +18406,11 @@
           <t>스너글 허거블 코튼 클린 앤 케어 캡슐세제</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7771483157?itemId=28604973749&amp;vendorItemId=95548520771</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>20000</v>
       </c>
@@ -18136,7 +18524,11 @@
           <t>올클린 냄새제거 초고농축 캡슐 세탁세제</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9655016135</t>
+        </is>
+      </c>
       <c r="H47" t="n">
         <v>7800</v>
       </c>
@@ -18250,7 +18642,11 @@
           <t>비트 캡슐 실내건조 캡슐세제 그린 플로럴향</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7674477942</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>13530</v>
       </c>
@@ -18359,7 +18755,11 @@
           <t>리큐 모락셀라 악취케어 실내건조 캡슐세제</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9726339807</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>12290</v>
       </c>
@@ -18473,7 +18873,11 @@
           <t>[커클랜드 시그니처] 커클랜드 울트라클린팩세제 140PC</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8363764498</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>29990</v>
       </c>
@@ -18587,7 +18991,11 @@
           <t>테크 딥클린 초고농축 캡슐세제</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8710604087</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>9810</v>
       </c>
@@ -18701,7 +19109,11 @@
           <t>다우니 초고농축 호텔 컬렉션 섬유유연제 미스티크 본품</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7026135886</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>15990</v>
       </c>
@@ -18810,7 +19222,11 @@
           <t>스너글 초고농축 섬유유연제 오리지널 허거블 코튼 본품</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1999003712</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>16700</v>
       </c>
@@ -18919,7 +19335,11 @@
           <t>피죤 레귤러 섬유유연제 핑크로즈 본품</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/142412365</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>16160</v>
       </c>
@@ -19028,7 +19448,11 @@
           <t>다우니 초고농축 호텔 컬렉션 섬유유연제 미스티크 리필</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8276935584</t>
+        </is>
+      </c>
       <c r="H55" t="n">
         <v>22710</v>
       </c>
@@ -19137,7 +19561,11 @@
           <t>다우니 업그레이드 섬유유연제 로맨스 본품</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1920077628</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>30710</v>
       </c>
@@ -19246,7 +19674,11 @@
           <t>다우니 실내건조 초고농축 섬유유연제 프레시 클린 본품</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8938973449</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>7200</v>
       </c>
@@ -19360,7 +19792,11 @@
           <t>피지 모락셀라 실내건조 섬유유연제 뽀송한 코튼향</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9531514933</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>13030</v>
       </c>
@@ -19469,7 +19905,11 @@
           <t>스너글 초고농축 섬유유연제 오리지널 허거블 코튼 리필</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6715891271</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>11610</v>
       </c>
@@ -19573,7 +20013,11 @@
           <t>실내건조 섬유유연제 에이프릴향 대용량 유연제</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9701967890</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>6890</v>
       </c>
@@ -19687,7 +20131,11 @@
           <t>스너글 섬유유연제 햇빛건조향 허거블 선샤인 본품</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9150772617</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>16000</v>
       </c>
@@ -19796,7 +20244,11 @@
           <t>다우니 호텔 컬렉션 화이트티 초고농축 섬유유연제 본품</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9235174023</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>11900</v>
       </c>
@@ -19910,7 +20362,11 @@
           <t>피죤 레귤러 섬유유연제 핑크로즈 리필</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7751136354?itemId=6825530960&amp;vendorItemId=3046244387</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>8740</v>
       </c>
@@ -20024,7 +20480,11 @@
           <t>아우라 초고농축 섬유유연제 윌유메리미 리필</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/196383388</t>
+        </is>
+      </c>
       <c r="H64" t="n">
         <v>10450</v>
       </c>
@@ -20133,7 +20593,11 @@
           <t>다우니 섬유유연제 에이프릴 프레쉬 본품</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7812055810</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>22900</v>
       </c>
@@ -20247,7 +20711,11 @@
           <t>스너글 고농축 섬유유연제 블루 스파클 플러스 본품</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7518506015</t>
+        </is>
+      </c>
       <c r="H66" t="n">
         <v>13600</v>
       </c>
@@ -20361,7 +20829,11 @@
           <t>아우라 7일 향기지속 윌유메리미 플러스 섬유유연제 본품</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7108273296</t>
+        </is>
+      </c>
       <c r="H67" t="n">
         <v>15430</v>
       </c>
@@ -20470,7 +20942,11 @@
           <t>아우라 7일 향기지속 섬유유연제 스모키머스크 플러스 본품</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/14828953</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>15420</v>
       </c>
@@ -20579,7 +21055,11 @@
           <t>스너글 허거블 선샤인 섬유유연제 햇빛건조향 리필</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6247825823</t>
+        </is>
+      </c>
       <c r="H69" t="n">
         <v>9710</v>
       </c>
@@ -20693,7 +21173,11 @@
           <t>다우니 고농축 섬유유연제 화이트티와 릴리 본품</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6724191008</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>15770</v>
       </c>
@@ -20802,7 +21286,11 @@
           <t>위칙 소독 섬유유연제 본품</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7429410266</t>
+        </is>
+      </c>
       <c r="H71" t="n">
         <v>20170</v>
       </c>
@@ -20911,7 +21399,11 @@
           <t>샤프란 플러스 섬유유연제 릴렉싱아로마 본품</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/11906922</t>
+        </is>
+      </c>
       <c r="H72" t="n">
         <v>15670</v>
       </c>
@@ -21020,7 +21512,11 @@
           <t>피죤 초고농축 시그니처 섬유유연제 미스틱레인 리필</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9331500027</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>10940</v>
       </c>
@@ -21129,7 +21625,11 @@
           <t>피지 모락셀라 실내건조 섬유유연제 뽀송한 코튼향 리필</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9592023573</t>
+        </is>
+      </c>
       <c r="H74" t="n">
         <v>14670</v>
       </c>
@@ -21238,7 +21738,11 @@
           <t>다우니 고농축 섬유유연제 아로마플로럴 본품</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/5428609074</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>27980</v>
       </c>
@@ -21347,7 +21851,11 @@
           <t>르샤트라1802 인퓨전 섬유유연제 피오니부케 본품</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8367276124</t>
+        </is>
+      </c>
       <c r="H76" t="n">
         <v>19660</v>
       </c>
@@ -21456,7 +21964,11 @@
           <t>페브리즈 항균플러스 섬유탈취제 깨끗한향 본품</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7677851491</t>
+        </is>
+      </c>
       <c r="H77" t="n">
         <v>13970</v>
       </c>
@@ -21565,7 +22077,11 @@
           <t>다우니 호텔 컬렉션 섬유스프레이 미스티크 향 본품</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9366358895</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>17070</v>
       </c>
@@ -21679,7 +22195,11 @@
           <t>페브리즈 섬유탈취제 다우니 에이프릴향 본품</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7802255498</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>12210</v>
       </c>
@@ -21788,7 +22308,11 @@
           <t>란도린 섬유탈취제 클래식 플로랄</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9481251242</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>15500</v>
       </c>
@@ -21902,7 +22426,11 @@
           <t>스너글 허거블 선샤인 퀵 드라이 섬유탈취제 본품</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8856289949?itemId=25820880234&amp;vendorItemId=92807808358</t>
+        </is>
+      </c>
       <c r="H81" t="n">
         <v>8890</v>
       </c>
@@ -22011,7 +22539,11 @@
           <t>페브리즈 섬유탈취제 은은한 꽃향 본품</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7837875730</t>
+        </is>
+      </c>
       <c r="H82" t="n">
         <v>11090</v>
       </c>
@@ -22120,7 +22652,11 @@
           <t>피지 모락셀라 섬유탈취제 뽀송한 코튼향 본품</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9273239756</t>
+        </is>
+      </c>
       <c r="H83" t="n">
         <v>6760</v>
       </c>
@@ -22229,7 +22765,11 @@
           <t>페브리즈 섬유탈취제 상쾌한향 본품</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7797646398</t>
+        </is>
+      </c>
       <c r="H84" t="n">
         <v>12020</v>
       </c>
@@ -22338,7 +22878,11 @@
           <t>피죤 스프레이 강력 섬유탈취제 옐로미모사</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/4842103286</t>
+        </is>
+      </c>
       <c r="H85" t="n">
         <v>13340</v>
       </c>
@@ -22447,7 +22991,11 @@
           <t>페브리즈 섬유탈취제 맨 쿨 아쿠아향 본품</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7837874607</t>
+        </is>
+      </c>
       <c r="H86" t="n">
         <v>9620</v>
       </c>
@@ -22561,7 +23109,11 @@
           <t>스너글 블루밍 부케 더블 소프트 섬유탈취제 본품</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7837874712</t>
+        </is>
+      </c>
       <c r="H87" t="n">
         <v>8620</v>
       </c>
@@ -22670,7 +23222,11 @@
           <t>스너글 스파클링 시트러스 더블 소프트 섬유탈취제 본품</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8856289948</t>
+        </is>
+      </c>
       <c r="H88" t="n">
         <v>9240</v>
       </c>
@@ -22779,7 +23335,11 @@
           <t>다우니 호텔 컬렉션 섬유스프레이 화이트티 향 본품</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9366444660</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>7500</v>
       </c>
@@ -22888,7 +23448,11 @@
           <t>페브리즈 섬유탈취제 다우니 실내건조 프레시클린향 본품</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7797650176</t>
+        </is>
+      </c>
       <c r="H90" t="n">
         <v>14460</v>
       </c>
@@ -22997,7 +23561,11 @@
           <t>페브리즈 섬유탈취제 강력탈취 상쾌한향 리필</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8374199262</t>
+        </is>
+      </c>
       <c r="H91" t="n">
         <v>11080</v>
       </c>
@@ -23106,7 +23674,11 @@
           <t>페브리즈 섬유탈취제 다우니 에이프릴향 리필</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7510800117</t>
+        </is>
+      </c>
       <c r="H92" t="n">
         <v>2900</v>
       </c>
@@ -23215,7 +23787,11 @@
           <t>다우니 호텔 컬렉션 섬유스프레이 웜코튼향 본품</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9366361175</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>14460</v>
       </c>
@@ -23324,7 +23900,11 @@
           <t>페브리즈 항균 플러스 섬유탈취제 산뜻한향 본품</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7759465715</t>
+        </is>
+      </c>
       <c r="H94" t="n">
         <v>12500</v>
       </c>
@@ -23438,7 +24018,11 @@
           <t>코코도르 패브릭 퍼퓸 섬유탈취제 우디호텔 본품</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8599376235</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>8910</v>
       </c>
@@ -23547,7 +24131,11 @@
           <t>르샤트라1802 섬유탈취제 피오니부케향 본품</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9737456651</t>
+        </is>
+      </c>
       <c r="H96" t="n">
         <v>7910</v>
       </c>
@@ -23656,7 +24244,11 @@
           <t>페브리즈 섬유 탈취제 깨끗한 향 리필</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7837875900?itemId=15110461853&amp;vendorItemId=85760410273</t>
+        </is>
+      </c>
       <c r="H97" t="n">
         <v>10260</v>
       </c>
@@ -23765,7 +24357,11 @@
           <t>부케가르니 섬유탈취제 베이비파우더 본품</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7851681710</t>
+        </is>
+      </c>
       <c r="H98" t="n">
         <v>9900</v>
       </c>
@@ -23874,7 +24470,11 @@
           <t>스너글 블루밍 부케 더블 소프트 섬유탈취제 본품</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8202419115</t>
+        </is>
+      </c>
       <c r="H99" t="n">
         <v>3500</v>
       </c>
@@ -23988,7 +24588,11 @@
           <t>아우라 퍼퓸 섬유탈취제 미스틱 문라이즈 본품</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8391385503</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>9590</v>
       </c>
@@ -24097,7 +24701,11 @@
           <t>아우라 섬유 향수 본품 윌유메리미</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9716584881</t>
+        </is>
+      </c>
       <c r="H101" t="n">
         <v>12240</v>
       </c>
@@ -24206,7 +24814,11 @@
           <t>트리오 베이킹소다를 담은 주방세제</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7031130231</t>
+        </is>
+      </c>
       <c r="H102" t="n">
         <v>8450</v>
       </c>
@@ -24315,7 +24927,11 @@
           <t>뷰카 베이킹소다 주방세제 레몬버베나향</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7589391826</t>
+        </is>
+      </c>
       <c r="H103" t="n">
         <v>13560</v>
       </c>
@@ -24424,7 +25040,11 @@
           <t>[비건라이프] 세이프 천연미네랄 주방세제 오리지널</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/80924</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>11050</v>
       </c>
@@ -24533,7 +25153,11 @@
           <t>맘스럽 레몬 주방세제 베이킹소다 특대용량 레몬향 과일 채소용 중성 세제</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9305171629</t>
+        </is>
+      </c>
       <c r="H105" t="n">
         <v>7140</v>
       </c>
@@ -24642,7 +25266,11 @@
           <t>자연퐁 찌든때 걱정없는 솔잎 파워워시 주방세제 용기형</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7925775685</t>
+        </is>
+      </c>
       <c r="H106" t="n">
         <v>9100</v>
       </c>
@@ -24751,7 +25379,11 @@
           <t>트리오 베이킹소다 담은 퓨어허브향 주방세제</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9707279838</t>
+        </is>
+      </c>
       <c r="H107" t="n">
         <v>3200</v>
       </c>
@@ -24865,7 +25497,11 @@
           <t>프로쉬 주방세제 알로에베라</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8403347749</t>
+        </is>
+      </c>
       <c r="H108" t="n">
         <v>5590</v>
       </c>
@@ -24979,7 +25615,11 @@
           <t>[비건라이프] 자연퐁 찌든때 걱정없는 솔잎 주방세제 용기형 리필</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7878925549</t>
+        </is>
+      </c>
       <c r="H109" t="n">
         <v>15100</v>
       </c>
@@ -25088,7 +25728,11 @@
           <t>슈가버블 친환경 주방세제 레몬 크러쉬</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7136884232</t>
+        </is>
+      </c>
       <c r="H110" t="n">
         <v>3900</v>
       </c>
@@ -25202,7 +25846,11 @@
           <t>탐사 라임 주방세제</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7632373677</t>
+        </is>
+      </c>
       <c r="H111" t="n">
         <v>6500</v>
       </c>
@@ -25311,7 +25959,11 @@
           <t>프로쉬 식기세척기 린스</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8627561762?itemId=25248625355&amp;vendorItemId=92416024733</t>
+        </is>
+      </c>
       <c r="H112" t="n">
         <v>12300</v>
       </c>
@@ -25425,7 +26077,11 @@
           <t>프릴 시크릿오브 베이킹소다 주방세제 상큼한 오렌지향</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8202659515</t>
+        </is>
+      </c>
       <c r="H113" t="n">
         <v>7540</v>
       </c>
@@ -25539,7 +26195,11 @@
           <t>주방세제 베이킹소다 대용량주방세제 레몬향</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9577065924</t>
+        </is>
+      </c>
       <c r="H114" t="n">
         <v>7080</v>
       </c>
@@ -25653,7 +26313,11 @@
           <t>자연퐁 스팀워시 식기세척기용 액체세제</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7325899154?itemId=19713363478&amp;vendorItemId=88356717131</t>
+        </is>
+      </c>
       <c r="H115" t="n">
         <v>13980</v>
       </c>
@@ -25767,7 +26431,11 @@
           <t>크로바 골드퐁 주방세제</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9028328561</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>10750</v>
       </c>
@@ -25876,7 +26544,11 @@
           <t>주방용 세제 베이킹소다 주방세제 레몬향</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9701090891</t>
+        </is>
+      </c>
       <c r="H117" t="n">
         <v>4670</v>
       </c>
@@ -25985,7 +26657,11 @@
           <t>프릴 시크릿오브 베이킹소다 주방세제 상큼한 오렌지향</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8189756332?itemId=23433588846&amp;vendorItemId=90460524397</t>
+        </is>
+      </c>
       <c r="H118" t="n">
         <v>8130</v>
       </c>
@@ -26094,7 +26770,11 @@
           <t>주방세제 베이킹소다 과일 야채 식기세척 대용량 주방 세제</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9629569396</t>
+        </is>
+      </c>
       <c r="H119" t="n">
         <v>6920</v>
       </c>
@@ -26203,7 +26883,11 @@
           <t>탐사 주방세제 리필</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6631315054</t>
+        </is>
+      </c>
       <c r="H120" t="n">
         <v>4280</v>
       </c>
@@ -26312,7 +26996,11 @@
           <t>탐사 클린퐁 주방세제</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7835456914</t>
+        </is>
+      </c>
       <c r="H121" t="n">
         <v>9780</v>
       </c>
@@ -26421,7 +27109,11 @@
           <t>참그린 레몬 녹차 뽀드득 어드밴스 주방세제 리필</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7867434239</t>
+        </is>
+      </c>
       <c r="H122" t="n">
         <v>8930</v>
       </c>
@@ -26530,7 +27222,11 @@
           <t>트리오 항균 주방세제</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6499690442</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>15890</v>
       </c>
@@ -26644,7 +27340,11 @@
           <t>퐁퐁 베이킹소다 주방세제 깔끔한 민트향 리필형</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9737456493</t>
+        </is>
+      </c>
       <c r="H124" t="n">
         <v>5650</v>
       </c>
@@ -26753,7 +27453,11 @@
           <t>퐁퐁 오렌지 오일 담은 친환경 주방세제 기분 좋은 오렌지향 리필</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9716584862</t>
+        </is>
+      </c>
       <c r="H125" t="n">
         <v>4700</v>
       </c>
@@ -26862,7 +27566,11 @@
           <t>탐사 베이킹소다 주방세제 레몬향</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/323587276</t>
+        </is>
+      </c>
       <c r="H126" t="n">
         <v>5490</v>
       </c>
@@ -26971,7 +27679,11 @@
           <t>하이포메디 뿌리는 살균소독제</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/4389476579</t>
+        </is>
+      </c>
       <c r="H127" t="n">
         <v>23800</v>
       </c>
@@ -27080,7 +27792,11 @@
           <t>클로시딘+정제수100ml+투약병100ml세트 링웜 턱드름 강아지 피부 및 상처 소독</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9752553730?itemId=29202290875&amp;vendorItemId=96122580472</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>10800</v>
       </c>
@@ -27194,7 +27910,11 @@
           <t>탐사 살균 소독 스프레이 500ml + 리필 1L</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/5157468347</t>
+        </is>
+      </c>
       <c r="H129" t="n">
         <v>9100</v>
       </c>
@@ -27303,7 +28023,11 @@
           <t>더블유제약 크레솔 비누액</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8791671127?itemId=25681432151&amp;vendorItemId=92670765899</t>
+        </is>
+      </c>
       <c r="H130" t="n">
         <v>6000</v>
       </c>
@@ -27417,7 +28141,11 @@
           <t>하이포메디 뿌리는 살균소독제 리필</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8367274839</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>19800</v>
       </c>
@@ -27526,7 +28254,11 @@
           <t>크로바 퓨톨 뿌리는 손소독제 살균소독제 리필</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7755132390?itemId=12022296896&amp;vendorItemId=79294612355</t>
+        </is>
+      </c>
       <c r="H132" t="n">
         <v>11910</v>
       </c>
@@ -27640,7 +28372,11 @@
           <t>진로발효 바이오크린콜 1L 2개+450ml 1개 뿌리는 살균 소독제 에탄올 75%</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9074733852?itemId=26654135361&amp;vendorItemId=93626619607</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>21000</v>
       </c>
@@ -27749,7 +28485,11 @@
           <t>주방 위생 세정제 쎄니크로 1L 야채 과일 소독제 식품용 세척제</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8607437249?itemId=24708429188&amp;vendorItemId=95611188335</t>
+        </is>
+      </c>
       <c r="H134" t="n">
         <v>5360</v>
       </c>
@@ -27858,7 +28598,11 @@
           <t>랩신 V3 항균 스프레이</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6939595123</t>
+        </is>
+      </c>
       <c r="H135" t="n">
         <v>14200</v>
       </c>
@@ -27972,7 +28716,11 @@
           <t>크로바 퓨톨 살균소독제 (의약외품) 휴대용 뿌리는 손소독제 50ml</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/2015524793?itemId=3743360754&amp;vendorItemId=71728517025</t>
+        </is>
+      </c>
       <c r="H136" t="n">
         <v>9910</v>
       </c>
@@ -28081,7 +28829,11 @@
           <t>[베어시스템] 크린콜1L 2개+분무기 공병 1개 뿌리는 소독제</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9215641931</t>
+        </is>
+      </c>
       <c r="H137" t="n">
         <v>12300</v>
       </c>
@@ -28195,7 +28947,11 @@
           <t>국대스타 살균소독제 리필용</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7072046199?itemId=17564772254&amp;vendorItemId=93869784417</t>
+        </is>
+      </c>
       <c r="H138" t="n">
         <v>34890</v>
       </c>
@@ -28304,7 +29060,11 @@
           <t>AWAS 이도소독용에탄올 항균 살균 알콜 소독스프레이</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9514047554</t>
+        </is>
+      </c>
       <c r="H139" t="n">
         <v>13300</v>
       </c>
@@ -28418,7 +29178,11 @@
           <t>크로바 바이오크린웰 살균소독제 주정알콜 뿌리는소독제 소독용에탄올</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8968251645?itemId=26834417944&amp;vendorItemId=70340399934</t>
+        </is>
+      </c>
       <c r="H140" t="n">
         <v>51910</v>
       </c>
@@ -28532,7 +29296,11 @@
           <t>메디록스 S 일반용 고수준 살균 소독제 탈취제 리필</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1268425384</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>17800</v>
       </c>
@@ -28641,7 +29409,11 @@
           <t>메디록스 S 일반용 고수준 살균 소독 스프레이</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/327279260</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>7210</v>
       </c>
@@ -28750,7 +29522,11 @@
           <t>살균 소독 탈취 차아염소산수(미산성) 세이프앤케어 20리터(Kg) HOCL 70~80ppm</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/4603744195</t>
+        </is>
+      </c>
       <c r="H143" t="n">
         <v>19350</v>
       </c>
@@ -28859,7 +29635,11 @@
           <t>탐사 살균 소독 스프레이 본품</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/5157468448</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>8990</v>
       </c>
@@ -28968,7 +29748,11 @@
           <t>탐사 곡물발효에탄올 함유 살균 소독제</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8618233939</t>
+        </is>
+      </c>
       <c r="H145" t="n">
         <v>8010</v>
       </c>
@@ -29077,7 +29861,11 @@
           <t>네이처러브메레 퍼펙트 에탄올 스프레이</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9531463873</t>
+        </is>
+      </c>
       <c r="H146" t="n">
         <v>5770</v>
       </c>
@@ -29186,7 +29974,11 @@
           <t>아가페케어 살균 소독제</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1460182327</t>
+        </is>
+      </c>
       <c r="H147" t="n">
         <v>10440</v>
       </c>
@@ -29300,7 +30092,11 @@
           <t>진로발효 살균소독 75% 바이오크린콜 1450ml 세트</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7828123872</t>
+        </is>
+      </c>
       <c r="H148" t="n">
         <v>11600</v>
       </c>
@@ -29414,7 +30210,11 @@
           <t>진로발효 바이오 크린콜 살균소독제</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7856288030</t>
+        </is>
+      </c>
       <c r="H149" t="n">
         <v>21290</v>
       </c>
@@ -29523,7 +30323,11 @@
           <t>탐사 살균 소독 스프레이 리필 4L</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/5157468423</t>
+        </is>
+      </c>
       <c r="H150" t="n">
         <v>8990</v>
       </c>
@@ -29632,7 +30436,11 @@
           <t>랩신 V3 항균 스프레이 살균제</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6939595123?itemId=14118068565&amp;vendorItemId=81365023566</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>14200</v>
       </c>
@@ -30336,7 +31144,11 @@
           <t>nimin 요식 물때 제거제 유리 물때 닦는 크림 화장실 거울 주방 샤워부스 주방 다용도 클리너 대용량, 450g, 1개</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9515051799?itemId=28358481548&amp;vendorItemId=94976541972</t>
+        </is>
+      </c>
       <c r="H157" t="n">
         <v>9900</v>
       </c>
@@ -31394,7 +32206,11 @@
           <t>락퐁 욕실 청소세제 코튼향, 4L, 1개</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7870197945?itemId=21497701535&amp;vendorItemId=70384401378</t>
+        </is>
+      </c>
       <c r="H166" t="n">
         <v>12580</v>
       </c>
@@ -37172,7 +37988,11 @@
           <t>아로퓸 향기 부스터 허니드 엑스트라, 500g, 1개</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8308867067</t>
+        </is>
+      </c>
       <c r="H215" t="n">
         <v>11950</v>
       </c>
@@ -37640,7 +38460,11 @@
           <t>아로퓸 향기 부스터 스윗 샤인, 500g, 1개</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8308872271?itemId=23973816647&amp;vendorItemId=88684518486</t>
+        </is>
+      </c>
       <c r="H219" t="n">
         <v>11950</v>
       </c>
@@ -47714,7 +48538,11 @@
           <t>랩신 V3 항균 스프레이 살균제</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6939595123?itemId=14118068565&amp;vendorItemId=81365023566</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>14200</v>
       </c>
@@ -47828,7 +48656,11 @@
           <t>탐사 살균 소독 스프레이 리필 4L</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/5157468423</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>8990</v>
       </c>
@@ -47937,7 +48769,11 @@
           <t>진로발효 바이오 크린콜 살균소독제</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7856288030</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>21290</v>
       </c>
@@ -48046,7 +48882,11 @@
           <t>진로발효 살균소독 75% 바이오크린콜 1450ml 세트</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7828123872</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>11600</v>
       </c>
@@ -48160,7 +49000,11 @@
           <t>아가페케어 살균 소독제</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1460182327</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>10440</v>
       </c>
@@ -48274,7 +49118,11 @@
           <t>네이처러브메레 퍼펙트 에탄올 스프레이</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9531463873</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>5770</v>
       </c>
@@ -48383,7 +49231,11 @@
           <t>탐사 곡물발효에탄올 함유 살균 소독제</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8618233939</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>8010</v>
       </c>
@@ -48492,7 +49344,11 @@
           <t>탐사 살균 소독 스프레이 본품</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/5157468448</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>8990</v>
       </c>
@@ -48601,7 +49457,11 @@
           <t>살균 소독 탈취 차아염소산수(미산성) 세이프앤케어 20리터(Kg) HOCL 70~80ppm</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/4603744195</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>19350</v>
       </c>
@@ -48710,7 +49570,11 @@
           <t>메디록스 S 일반용 고수준 살균 소독 스프레이</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/327279260</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>7210</v>
       </c>
@@ -48819,7 +49683,11 @@
           <t>메디록스 S 일반용 고수준 살균 소독제 탈취제 리필</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1268425384</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>17800</v>
       </c>
@@ -48928,7 +49796,11 @@
           <t>크로바 바이오크린웰 살균소독제 주정알콜 뿌리는소독제 소독용에탄올</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8968251645?itemId=26834417944&amp;vendorItemId=70340399934</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>51910</v>
       </c>
@@ -49042,7 +49914,11 @@
           <t>AWAS 이도소독용에탄올 항균 살균 알콜 소독스프레이</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9514047554</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>13300</v>
       </c>
@@ -49156,7 +50032,11 @@
           <t>국대스타 살균소독제 리필용</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7072046199?itemId=17564772254&amp;vendorItemId=93869784417</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>34890</v>
       </c>
@@ -49265,7 +50145,11 @@
           <t>[베어시스템] 크린콜1L 2개+분무기 공병 1개 뿌리는 소독제</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9215641931</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>12300</v>
       </c>
@@ -49379,7 +50263,11 @@
           <t>크로바 퓨톨 살균소독제 (의약외품) 휴대용 뿌리는 손소독제 50ml</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/2015524793?itemId=3743360754&amp;vendorItemId=71728517025</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>9910</v>
       </c>
@@ -49488,7 +50376,11 @@
           <t>랩신 V3 항균 스프레이</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6939595123</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>14200</v>
       </c>
@@ -49602,7 +50494,11 @@
           <t>주방 위생 세정제 쎄니크로 1L 야채 과일 소독제 식품용 세척제</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8607437249?itemId=24708429188&amp;vendorItemId=95611188335</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>5360</v>
       </c>
@@ -49711,7 +50607,11 @@
           <t>진로발효 바이오크린콜 1L 2개+450ml 1개 뿌리는 살균 소독제 에탄올 75%</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9074733852?itemId=26654135361&amp;vendorItemId=93626619607</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>21000</v>
       </c>
@@ -49820,7 +50720,11 @@
           <t>크로바 퓨톨 뿌리는 손소독제 살균소독제 리필</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7755132390?itemId=12022296896&amp;vendorItemId=79294612355</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>11910</v>
       </c>
@@ -49934,7 +50838,11 @@
           <t>하이포메디 뿌리는 살균소독제 리필</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8367274839</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>19800</v>
       </c>
@@ -50043,7 +50951,11 @@
           <t>더블유제약 크레솔 비누액</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8791671127?itemId=25681432151&amp;vendorItemId=92670765899</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>6000</v>
       </c>
@@ -50157,7 +51069,11 @@
           <t>탐사 살균 소독 스프레이 500ml + 리필 1L</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/5157468347</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>9100</v>
       </c>
@@ -50266,7 +51182,11 @@
           <t>클로시딘+정제수100ml+투약병100ml세트 링웜 턱드름 강아지 피부 및 상처 소독</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9752553730?itemId=29202290875&amp;vendorItemId=96122580472</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>10800</v>
       </c>
@@ -50380,7 +51300,11 @@
           <t>하이포메디 뿌리는 살균소독제</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/4389476579</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>23800</v>
       </c>
@@ -50635,7 +51559,11 @@
           <t>다우니 초고농축 호텔 컬렉션 섬유유연제 미스티크 본품</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7026135886</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>15990</v>
       </c>
@@ -50744,7 +51672,11 @@
           <t>스너글 초고농축 섬유유연제 오리지널 허거블 코튼 본품</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1999003712</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>16700</v>
       </c>
@@ -50853,7 +51785,11 @@
           <t>피죤 레귤러 섬유유연제 핑크로즈 본품</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/142412365</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>16160</v>
       </c>
@@ -50962,7 +51898,11 @@
           <t>다우니 초고농축 호텔 컬렉션 섬유유연제 미스티크 리필</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8276935584</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>22710</v>
       </c>
@@ -51071,7 +52011,11 @@
           <t>다우니 업그레이드 섬유유연제 로맨스 본품</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/1920077628</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>30710</v>
       </c>
@@ -51180,7 +52124,11 @@
           <t>다우니 실내건조 초고농축 섬유유연제 프레시 클린 본품</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8938973449</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>7200</v>
       </c>
@@ -51294,7 +52242,11 @@
           <t>피지 모락셀라 실내건조 섬유유연제 뽀송한 코튼향</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9531514933</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>13030</v>
       </c>
@@ -51403,7 +52355,11 @@
           <t>스너글 초고농축 섬유유연제 오리지널 허거블 코튼 리필</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6715891271</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>11610</v>
       </c>
@@ -51507,7 +52463,11 @@
           <t>실내건조 섬유유연제 에이프릴향 대용량 유연제</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9701967890</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>6890</v>
       </c>
@@ -51621,7 +52581,11 @@
           <t>스너글 섬유유연제 햇빛건조향 허거블 선샤인 본품</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9150772617</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>16000</v>
       </c>
@@ -51730,7 +52694,11 @@
           <t>다우니 호텔 컬렉션 화이트티 초고농축 섬유유연제 본품</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9235174023</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>11900</v>
       </c>
@@ -51844,7 +52812,11 @@
           <t>피죤 레귤러 섬유유연제 핑크로즈 리필</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7751136354?itemId=6825530960&amp;vendorItemId=3046244387</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>8740</v>
       </c>
@@ -51958,7 +52930,11 @@
           <t>아우라 초고농축 섬유유연제 윌유메리미 리필</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/196383388</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>10450</v>
       </c>
@@ -52067,7 +53043,11 @@
           <t>다우니 섬유유연제 에이프릴 프레쉬 본품</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7812055810</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>22900</v>
       </c>
@@ -52181,7 +53161,11 @@
           <t>스너글 고농축 섬유유연제 블루 스파클 플러스 본품</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7518506015</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>13600</v>
       </c>
@@ -52295,7 +53279,11 @@
           <t>아우라 7일 향기지속 윌유메리미 플러스 섬유유연제 본품</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7108273296</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>15430</v>
       </c>
@@ -52404,7 +53392,11 @@
           <t>아우라 7일 향기지속 섬유유연제 스모키머스크 플러스 본품</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/14828953</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>15420</v>
       </c>
@@ -52513,7 +53505,11 @@
           <t>스너글 허거블 선샤인 섬유유연제 햇빛건조향 리필</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6247825823</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>9710</v>
       </c>
@@ -52627,7 +53623,11 @@
           <t>다우니 고농축 섬유유연제 화이트티와 릴리 본품</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6724191008</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>15770</v>
       </c>
@@ -52736,7 +53736,11 @@
           <t>위칙 소독 섬유유연제 본품</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7429410266</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>20170</v>
       </c>
@@ -52845,7 +53849,11 @@
           <t>샤프란 플러스 섬유유연제 릴렉싱아로마 본품</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/11906922</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>15670</v>
       </c>
@@ -52954,7 +53962,11 @@
           <t>피죤 초고농축 시그니처 섬유유연제 미스틱레인 리필</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9331500027</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>10940</v>
       </c>
@@ -53063,7 +54075,11 @@
           <t>피지 모락셀라 실내건조 섬유유연제 뽀송한 코튼향 리필</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9592023573</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>14670</v>
       </c>
@@ -53172,7 +54188,11 @@
           <t>다우니 고농축 섬유유연제 아로마플로럴 본품</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/5428609074</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>27980</v>
       </c>
@@ -53281,7 +54301,11 @@
           <t>르샤트라1802 인퓨전 섬유유연제 피오니부케 본품</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8367276124</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>19660</v>
       </c>
@@ -53536,7 +54560,11 @@
           <t>페브리즈 항균플러스 섬유탈취제 깨끗한향 본품</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7677851491</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>13970</v>
       </c>
@@ -53645,7 +54673,11 @@
           <t>다우니 호텔 컬렉션 섬유스프레이 미스티크 향 본품</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9366358895</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>17070</v>
       </c>
@@ -53759,7 +54791,11 @@
           <t>페브리즈 섬유탈취제 다우니 에이프릴향 본품</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7802255498</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>12210</v>
       </c>
@@ -53868,7 +54904,11 @@
           <t>란도린 섬유탈취제 클래식 플로랄</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9481251242</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>15500</v>
       </c>
@@ -53982,7 +55022,11 @@
           <t>스너글 허거블 선샤인 퀵 드라이 섬유탈취제 본품</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8856289949?itemId=25820880234&amp;vendorItemId=92807808358</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>8890</v>
       </c>
@@ -54091,7 +55135,11 @@
           <t>페브리즈 섬유탈취제 은은한 꽃향 본품</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7837875730</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>11090</v>
       </c>
@@ -54200,7 +55248,11 @@
           <t>피지 모락셀라 섬유탈취제 뽀송한 코튼향 본품</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9273239756</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>6760</v>
       </c>
@@ -54309,7 +55361,11 @@
           <t>페브리즈 섬유탈취제 상쾌한향 본품</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7797646398</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>12020</v>
       </c>
@@ -54418,7 +55474,11 @@
           <t>피죤 스프레이 강력 섬유탈취제 옐로미모사</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/4842103286</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>13340</v>
       </c>
@@ -54527,7 +55587,11 @@
           <t>페브리즈 섬유탈취제 맨 쿨 아쿠아향 본품</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7837874607</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>9620</v>
       </c>
@@ -54641,7 +55705,11 @@
           <t>스너글 블루밍 부케 더블 소프트 섬유탈취제 본품</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7837874712</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>8620</v>
       </c>
@@ -54750,7 +55818,11 @@
           <t>스너글 스파클링 시트러스 더블 소프트 섬유탈취제 본품</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8856289948</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>9240</v>
       </c>
@@ -54859,7 +55931,11 @@
           <t>다우니 호텔 컬렉션 섬유스프레이 화이트티 향 본품</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9366444660</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>7500</v>
       </c>
@@ -54968,7 +56044,11 @@
           <t>페브리즈 섬유탈취제 다우니 실내건조 프레시클린향 본품</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7797650176</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>14460</v>
       </c>
@@ -55077,7 +56157,11 @@
           <t>페브리즈 섬유탈취제 강력탈취 상쾌한향 리필</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8374199262</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>11080</v>
       </c>
@@ -55186,7 +56270,11 @@
           <t>페브리즈 섬유탈취제 다우니 에이프릴향 리필</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7510800117</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>2900</v>
       </c>
@@ -55295,7 +56383,11 @@
           <t>다우니 호텔 컬렉션 섬유스프레이 웜코튼향 본품</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9366361175</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>14460</v>
       </c>
@@ -55404,7 +56496,11 @@
           <t>페브리즈 항균 플러스 섬유탈취제 산뜻한향 본품</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7759465715</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>12500</v>
       </c>
@@ -55518,7 +56614,11 @@
           <t>코코도르 패브릭 퍼퓸 섬유탈취제 우디호텔 본품</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8599376235</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>8910</v>
       </c>
@@ -55627,7 +56727,11 @@
           <t>르샤트라1802 섬유탈취제 피오니부케향 본품</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9737456651</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>7910</v>
       </c>
@@ -55736,7 +56840,11 @@
           <t>페브리즈 섬유 탈취제 깨끗한 향 리필</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7837875900?itemId=15110461853&amp;vendorItemId=85760410273</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>10260</v>
       </c>
@@ -55845,7 +56953,11 @@
           <t>부케가르니 섬유탈취제 베이비파우더 본품</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7851681710</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>9900</v>
       </c>
@@ -55954,7 +57066,11 @@
           <t>스너글 블루밍 부케 더블 소프트 섬유탈취제 본품</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8202419115</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>3500</v>
       </c>
@@ -56068,7 +57184,11 @@
           <t>아우라 퍼퓸 섬유탈취제 미스틱 문라이즈 본품</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8391385503</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>9590</v>
       </c>
@@ -56177,7 +57297,11 @@
           <t>아우라 섬유 향수 본품 윌유메리미</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9716584881</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>12240</v>
       </c>
@@ -56432,7 +57556,11 @@
           <t>피지 모락셀라 냄새제거 세탁세제 코튼향</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8527004003</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>14650</v>
       </c>
@@ -56546,7 +57674,11 @@
           <t>탐사 파워워시 액체세제 본품</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/305732568</t>
+        </is>
+      </c>
       <c r="H3" t="n">
         <v>10990</v>
       </c>
@@ -56655,7 +57787,11 @@
           <t>액츠 퍼펙트 실내건조 일반용 프레시 플로럴향 액상세제 본품</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9711973763</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>9590</v>
       </c>
@@ -56764,7 +57900,11 @@
           <t>퍼실 딥클린 초미세세탁 라벤더젤 맥스 드럼용 액체세제 본품</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8971726601</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>13940</v>
       </c>
@@ -56873,7 +58013,11 @@
           <t>퍼실 딥클린 초미세세탁 라벤더젤 맥스 일반용 액체세제 리필</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9354349642</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>14920</v>
       </c>
@@ -56987,7 +58131,11 @@
           <t>피지 모락셀라 빨래쉰내 냄새제거 실내건조 세탁세제 코튼향 리필</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8542806480</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>14950</v>
       </c>
@@ -57096,7 +58244,11 @@
           <t>세탁세제 실내건조 라벤더향 액체세제 일반용 드럼용 세제</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9618034717</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>7570</v>
       </c>
@@ -57210,7 +58362,11 @@
           <t>리큐 진한겔 하이브리드 플로랄향 일반용 액상세제 리필</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/6616908158</t>
+        </is>
+      </c>
       <c r="H9" t="n">
         <v>18900</v>
       </c>
@@ -57319,7 +58475,11 @@
           <t>세탁세제 실내건조 액체세제 일반용 드럼용 세제</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9614568860</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>6980</v>
       </c>
@@ -57433,7 +58593,11 @@
           <t>스너글 블루스파클 플러스 실내건조 액상세탁세제 본품</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8457659514</t>
+        </is>
+      </c>
       <c r="H11" t="n">
         <v>14910</v>
       </c>
@@ -57542,7 +58706,11 @@
           <t>액체세제 빨래세제 실내건조 중성 액체 세탁 세제</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9116096390</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>7660</v>
       </c>
@@ -57656,7 +58824,11 @@
           <t>피지 모락셀라 실내건조 냄새제거 세탁세제 화이트머스크향 본품</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9219436965?itemId=27242368652&amp;vendorItemId=95181766755</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>14950</v>
       </c>
@@ -57765,7 +58937,11 @@
           <t>다우니 실내건조 초고농축 섬유유연제 프레시 클린 자스민향 리필</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8773985820?itemId=25523705270&amp;vendorItemId=91855119935</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>21990</v>
       </c>
@@ -57879,7 +59055,11 @@
           <t>비트 진드기 침투세탁 액상세제 일반용 본품</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/990781?itemId=17746812132&amp;vendorItemId=3000206661</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>31550</v>
       </c>
@@ -57993,7 +59173,11 @@
           <t>터치 라이트 고농축 세탁세제 라벤더</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8034891009</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>14750</v>
       </c>
@@ -58107,7 +59291,11 @@
           <t>퍼실 딥클린 초미세세탁 파워젤 맥스 드럼용 액체세제 본품</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9354362095</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>13850</v>
       </c>
@@ -58216,7 +59404,11 @@
           <t>봉쥬르끌레어 블랙젤 액체세제 라벤더향 실내건조 중성세제</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8416837413</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>6990</v>
       </c>
@@ -58325,7 +59517,11 @@
           <t>비트 때가쏙 진드기 일반 액상세제 리필</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/2299858861</t>
+        </is>
+      </c>
       <c r="H19" t="n">
         <v>19870</v>
       </c>
@@ -58434,7 +59630,11 @@
           <t>탐사 딥클린 코튼향 세탁세제 본품</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8915603116</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>4950</v>
       </c>
@@ -58543,7 +59743,11 @@
           <t>테크 베이킹소다 플러스 구연산 실내건조 액체세제 일반용 리필</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7825605298</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>17910</v>
       </c>
@@ -58652,7 +59856,11 @@
           <t>퍼실 엑스퍼트 실내건조 맥스 드럼용 액상세제 본품</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9414661283?itemId=27974996303&amp;vendorItemId=94932853898</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>13770</v>
       </c>
@@ -58761,7 +59969,11 @@
           <t>터치 고농축 액체세제 코델리아 세탁세제 3.05L 4개</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7206437724?itemId=18225908031&amp;vendorItemId=85155981677</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>19650</v>
       </c>
@@ -58870,7 +60082,11 @@
           <t>액츠 퍼펙트 실내건조 액상세제 리필</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/8123764928</t>
+        </is>
+      </c>
       <c r="H24" t="n">
         <v>20700</v>
       </c>
@@ -58979,7 +60195,11 @@
           <t>리큐 진한겔 하이브리드 드럼세탁기용 액상세제 플로럴 부케향 리필</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7235489530</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>18900</v>
       </c>
@@ -59088,7 +60308,11 @@
           <t>퍼실 딥클린 초미세세탁 라벤더젤 맥스 일반용 액체세제 본품</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9354362095?itemId=27967268511&amp;vendorItemId=94925214636</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>13940</v>
       </c>
@@ -63029,7 +64253,11 @@
           <t>nimin 요식 물때 제거제 유리 물때 닦는 크림 화장실 거울 주방 샤워부스 주방 다용도 클리너 대용량, 450g, 1개</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/9515051799?itemId=28358481548&amp;vendorItemId=94976541972</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>9900</v>
       </c>
@@ -64087,7 +65315,11 @@
           <t>락퐁 욕실 청소세제 코튼향, 4L, 1개</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.coupang.com/vp/products/7870197945?itemId=21497701535&amp;vendorItemId=70384401378</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>12580</v>
       </c>

--- a/쿠팡_11개카테고리_275개_제품목록.xlsx
+++ b/쿠팡_11개카테고리_275개_제품목록.xlsx
@@ -957,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1091,6 +1091,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1209,6 +1214,11 @@
           <t>Perfect Cleansing, Easy &amp; Clear, For clean and lively lifestyle, Dry Cleaning Detergent, 식물유래 계면활성제, 5가지 허브추출물, 드로피컬 꽃향, 저자극 중성세제; 쿠팡 순위 표기가 홈드라이세제 랭킹</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>울세제-19</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1327,6 +1337,11 @@
           <t>중성세제 | 일반/드럼 겸용 | 울/실크/면 등 세탁 | 액체형 / 호평받은 은은하고 포근한 비누 향</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>울세제-19</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3677,6 +3692,11 @@
       <c r="Z23" t="inlineStr">
         <is>
           <t>중성세제 | 손세탁/일반/드럼 겸용 | 울/실크/면/린넨 케어 | 52.6회 사용, 호평받은 은은하고 산뜻한 향</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>울세제-01</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4177,6 +4197,11 @@
       <c r="Z1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7190,6 +7215,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9259,6 +9289,11 @@
           <t>지퍼형 파우치 포장</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>캡슐세제-19</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9375,6 +9410,11 @@
       <c r="Z20" t="inlineStr">
         <is>
           <t>할인 표기 없음(정가 판매)</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>캡슐세제-18</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10226,6 +10266,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10816,6 +10861,11 @@
           <t>간편 섬유 향기 부스터 / 자수정 베리 / 쿠팡 상품 상세 화면 캡처</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>향기지속제-24</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10934,6 +10984,11 @@
           <t>고급스러운 향, 건조기 후에도 오래오래, 향기부스터 WHITE MUSK, 화이트 머스크 향, 다우니 with lenor; 동일 제품군 페이지로 추정(구성 옵션 상이 가능)</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>향기지속제-08</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11170,6 +11225,11 @@
           <t>쿠팡 상품 상세 화면 캡처. 다우니 브랜드의 향기부스터 3종 세트가 보이며, 보라/파랑/핑크 색상의 용기형 제품 이미지가 전면에 배치되어 있음. 가격 위에 '향기지속제 구매 8위' 문구가 표시됨. 최종 판매가 18,820원, 별점은 5점으로 보이고 리뷰 수는 584개. '한 달간 3,000명 이상 구매했어요' 문구가 있으며, 3개월 무이자(쿠팡 와우) 구매 안내와 장바구니 담기/바로구매 버튼; 제목에 3종 향(화이트머스크+화이트티+블루밍블라썸) 표기, 실제 판매단위 205g 1개(쿠팡 표기단가와 일치); 쿠팡 URL 매칭 신뢰도 보통(검색 결과·표기 차이 가능, 확인 권장)</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>향기지속제-06</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13056,6 +13116,11 @@
       <c r="Z25" t="inlineStr">
         <is>
           <t>간편 섬유 향기 부스터, 12주 지속되는 풍성한 향기로 호평</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>향기지속제-05</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z276"/>
+  <dimension ref="A1:AA276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13322,6 +13387,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15091,7 +15161,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9354362095</t>
+          <t>https://www.coupang.com/vp/products/9471905450?itemId=27967342446&amp;vendorItemId=94925286601</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -18256,6 +18326,11 @@
           <t>지퍼형 파우치 포장</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>캡슐세제-19</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -18374,6 +18449,11 @@
           <t>할인 표기 없음(정가 판매)</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>캡슐세제-18</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -28684,6 +28764,11 @@
           <t>25.jpg와 동일 제품으로 보이나 별도 상품 페이지(순위·리뷰수 다름)</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>살균소독제-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -30522,6 +30607,11 @@
           <t>09.jpg와 동일 제품으로 보이나 별도 상품 페이지(순위·리뷰수 다름)</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>살균소독제-17</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -30640,6 +30730,11 @@
           <t>유해세균 99.9% 제거 | 물때제거 | 비누때제거 | 거품타입 | 강력한 세정력 | 은은한 분향기</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>욕실세정제-16</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -32410,6 +32505,11 @@
           <t>유해세균 99.9% 제거 | 찌든때 제거 | 거품 타입 | 분사형 | 호평받은 쫀쫀한 거품 제형 | 강력한 세정력</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>욕실세정제-01</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -37012,6 +37112,11 @@
           <t>간편 섬유 향기 부스터 / 자수정 베리 / 쿠팡 상품 상세 화면 캡처</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>향기지속제-24</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -37130,6 +37235,11 @@
           <t>고급스러운 향, 건조기 후에도 오래오래, 향기부스터 WHITE MUSK, 화이트 머스크 향, 다우니 with lenor; 동일 제품군 페이지로 추정(구성 옵션 상이 가능)</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>향기지속제-08</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -37366,6 +37476,11 @@
           <t>쿠팡 상품 상세 화면 캡처. 다우니 브랜드의 향기부스터 3종 세트가 보이며, 보라/파랑/핑크 색상의 용기형 제품 이미지가 전면에 배치되어 있음. 가격 위에 '향기지속제 구매 8위' 문구가 표시됨. 최종 판매가 18,820원, 별점은 5점으로 보이고 리뷰 수는 584개. '한 달간 3,000명 이상 구매했어요' 문구가 있으며, 3개월 무이자(쿠팡 와우) 구매 안내와 장바구니 담기/바로구매 버튼; 제목에 3종 향(화이트머스크+화이트티+블루밍블라썸) 표기, 실제 판매단위 205g 1개(쿠팡 표기단가와 일치); 쿠팡 URL 매칭 신뢰도 보통(검색 결과·표기 차이 가능, 확인 권장)</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>향기지속제-06</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -39254,6 +39369,11 @@
           <t>간편 섬유 향기 부스터, 12주 지속되는 풍성한 향기로 호평</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>향기지속제-05</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -42903,6 +43023,11 @@
           <t>중성세제 | 손세탁/일반/드럼 겸용 | 울/실크/면/린넨 케어 | 52.6회 사용, 호평받은 은은하고 산뜻한 향</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>울세제-01</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -44556,6 +44681,11 @@
           <t>Perfect Cleansing, Easy &amp; Clear, For clean and lively lifestyle, Dry Cleaning Detergent, 식물유래 계면활성제, 5가지 허브추출물, 드로피컬 꽃향, 저자극 중성세제; 쿠팡 순위 표기가 홈드라이세제 랭킹</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>울세제-19</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -45262,6 +45392,11 @@
       <c r="Z276" t="inlineStr">
         <is>
           <t>중성세제 | 일반/드럼 겸용 | 울/실크/면 등 세탁 | 액체형 / 호평받은 은은하고 포근한 비누 향</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>울세제-19</t>
         </is>
       </c>
     </row>
@@ -45276,7 +45411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45408,6 +45543,11 @@
       <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
         </is>
       </c>
     </row>
@@ -48372,7 +48512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48506,6 +48646,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -48624,6 +48769,11 @@
           <t>09.jpg와 동일 제품으로 보이나 별도 상품 페이지(순위·리뷰수 다름)</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>살균소독제-17</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -50460,6 +50610,11 @@
       <c r="Z18" t="inlineStr">
         <is>
           <t>25.jpg와 동일 제품으로 보이나 별도 상품 페이지(순위·리뷰수 다름)</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>살균소독제-01</t>
         </is>
       </c>
     </row>
@@ -51393,7 +51548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51525,6 +51680,11 @@
       <c r="Z1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
         </is>
       </c>
     </row>
@@ -54394,7 +54554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54526,6 +54686,11 @@
       <c r="Z1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
         </is>
       </c>
     </row>
@@ -57390,7 +57555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57524,6 +57689,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -59293,7 +59463,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.coupang.com/vp/products/9354362095</t>
+          <t>https://www.coupang.com/vp/products/9471905450?itemId=27967342446&amp;vendorItemId=94925286601</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -60401,7 +60571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60533,6 +60703,11 @@
       <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
         </is>
       </c>
     </row>
@@ -63497,7 +63672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63631,6 +63806,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>중복(같은딜번호)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -63749,6 +63929,11 @@
           <t>유해세균 99.9% 제거 | 물때제거 | 비누때제거 | 거품타입 | 강력한 세정력 | 은은한 분향기</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>욕실세정제-16</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -65517,6 +65702,11 @@
       <c r="Z17" t="inlineStr">
         <is>
           <t>유해세균 99.9% 제거 | 찌든때 제거 | 거품 타입 | 분사형 | 호평받은 쫀쫀한 거품 제형 | 강력한 세정력</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>욕실세정제-01</t>
         </is>
       </c>
     </row>
